--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,13 +462,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.003596124989433735</v>
+        <v>-0.05738080549403934</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3116747399649242</v>
+        <v>0.1901864476540797</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.09458774622345122</v>
+        <v>-0.334411345138276</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1321160218432217</v>
+        <v>-0.4515127422304493</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2741985995614042</v>
+        <v>0.1657855310697237</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.01481711169924778</v>
+        <v>-0.3896408467290603</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>31.82880008435355</v>
+        <v>38.26711356670273</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2662481272915855</v>
+        <v>-0.05225062340570008</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2390235298603466</v>
+        <v>0.2867855675468388</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.290760335699372</v>
+        <v>-0.1039949166195374</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.698896877482867</v>
+        <v>-0.1474569613815934</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.333210081498019</v>
+        <v>0.1885986532312296</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8270309194577236</v>
+        <v>-0.2881780648603235</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>39.6863545023612</v>
+        <v>23.77178507797378</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02481998279203401</v>
+        <v>-0.1135750867107002</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2333490942429085</v>
+        <v>0.2475925548706103</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.05994001256531106</v>
+        <v>-0.4432642705731631</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.08697536020481363</v>
+        <v>-0.5958255892282754</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2351158163924901</v>
+        <v>0.2289298417458613</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.1098702844456093</v>
+        <v>-0.5153547055301345</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>38.41360504205348</v>
+        <v>46.56065077400039</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.03982846599552792</v>
+        <v>0.4485756263884246</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2290854195765797</v>
+        <v>0.3012961152534583</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.226234971267687</v>
+        <v>1.379915856515286</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.3343585716157465</v>
+        <v>2.38843889564446</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1616989964446542</v>
+        <v>0.1453962167027953</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.2566990176258922</v>
+        <v>3.238933971418036</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>40.92646902264178</v>
+        <v>41.01442263158227</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2454956179566394</v>
+        <v>0.5755023391592855</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2678042826430133</v>
+        <v>0.3119524267797033</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.9290069193358483</v>
+        <v>1.621386446559659</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.307250563934481</v>
+        <v>2.304733384771494</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1831125196730042</v>
+        <v>0.2012785927226414</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.396211825899333</v>
+        <v>2.992132268759538</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>49.3911730585604</v>
+        <v>39.83464638125394</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.4179322741609068</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.4130061712028598</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1.70263816724153</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2.694006930567936</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1721154887956907</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>5.132630378776264</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>39.64698417045254</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>